--- a/public/templates/Litmus_Bulk_Import_Master_Template.xlsx
+++ b/public/templates/Litmus_Bulk_Import_Master_Template.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Parameters syntax: 'Name:Unit:MinLimit:MaxLimit:Price'. Multiple parameters separated by semicolon ';'. Subcategories are comma-separated.</t>
+          <t>Parameters syntax: 'Name:Unit:MinLimit:MaxLimit:Price'. Multiple parameters separated by semicolon ';'. Subcategories are comma-separated. Optional 'displayOrder' sets the website priority (1 = shown first; 0 removes it).</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Enter comma-separated test names in 'tests' column. Tests must exist before package creation.</t>
+          <t>Enter comma-separated test names in 'tests' column. Tests must exist before package creation. Optional 'displayOrder' sets the website priority (1 = shown first; 0 removes it).</t>
         </is>
       </c>
     </row>
@@ -804,10 +804,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="139" customWidth="1" min="1" max="1"/>
+    <col width="222" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -824,12 +824,13 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="121" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Define test details, subcategories, and parameters. Use 'Name:Unit:Min:Max:Price' format for parameters separated by ';'.</t>
+          <t>INSTRUCTIONS: Define test details, subcategories, and parameters. Use 'Name:Unit:Min:Max:Price' format for parameters separated by ';'. Optional 'displayOrder' sets the website priority (1 = shown first; 0 removes it).</t>
         </is>
       </c>
     </row>
@@ -919,6 +920,11 @@
           <t>parameters</t>
         </is>
       </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>displayOrder</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -1006,6 +1012,11 @@
           <t>OPTIONAL</t>
         </is>
       </c>
+      <c r="R3" s="8" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1083,6 +1094,9 @@
           <t>Total Fat:%:3.0:8.0:180; Solids Not Fat (SNF):%:8.0:10.5:120; Density:g/ml:1.026:1.032:100</t>
         </is>
       </c>
+      <c r="R4" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -1155,6 +1169,9 @@
         <is>
           <t>Moisture Content:%:0:60.0:250; Fat on Dry Basis:%:45.0:70.0:300</t>
         </is>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1221,6 +1238,7 @@
           <t>Total Coliform Count:cfu/g:0:10:350; E. Coli Count:cfu/g:0:0:450</t>
         </is>
       </c>
+      <c r="R6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -1286,10 +1304,11 @@
           <t>Lead (Pb):ppm:0.0:0.1:400; Cadmium (Cd):ppm:0.0:0.05:400; Arsenic (As):ppm:0.0:0.1:450; Mercury (Hg):ppm:0.0:0.01:450</t>
         </is>
       </c>
+      <c r="R7" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1301,10 +1320,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="123" customWidth="1" min="1" max="1"/>
+    <col width="206" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="77" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -1316,12 +1335,13 @@
     <col width="115" customWidth="1" min="10" max="10"/>
     <col width="115" customWidth="1" min="11" max="11"/>
     <col width="51" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Bundle existing tests by providing comma-separated test names. Specify selling price and turnaround time.</t>
+          <t>INSTRUCTIONS: Bundle existing tests by providing comma-separated test names. Specify selling price and turnaround time. Optional 'displayOrder' sets the website priority (1 = shown first; 0 removes it).</t>
         </is>
       </c>
     </row>
@@ -1386,6 +1406,11 @@
           <t>image</t>
         </is>
       </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>displayOrder</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -1448,6 +1473,11 @@
           <t>OPTIONAL</t>
         </is>
       </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1504,6 +1534,9 @@
           <t>https://example.com/packages/dairy-standard.png</t>
         </is>
       </c>
+      <c r="M4" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -1556,10 +1589,11 @@
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
